--- a/assets/infobasica/planilhas/aula29_nivel3.xlsx
+++ b/assets/infobasica/planilhas/aula29_nivel3.xlsx
@@ -623,9 +623,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>ARRED(A2/25,4; 3) arrastada converte as medidas para polegadas e =(CONT.SE(A2:A16; "&gt;50,2")+CONT.SE(A2:A16; "&lt;49,8"))/CONT(A2:A16) dá o percentual reprovado.</f>
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>=ARRED(A2/25,4; 3) arrastada converte as medidas para polegadas e =(CONT.SE(A2:A16; "&gt;50,2")+CONT.SE(A2:A16; "&lt;49,8"))/CONT(A2:A16) dá o percentual reprovado.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -638,7 +639,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
